--- a/auditoria-transformadores-134/public/bases/Material_Pendente.xlsx
+++ b/auditoria-transformadores-134/public/bases/Material_Pendente.xlsx
@@ -4727,7 +4727,7 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr">
         <is>
-          <t>sem_fato</t>
+          <t>fora_da_janela</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">

--- a/auditoria-transformadores-134/public/bases/Material_Pendente.xlsx
+++ b/auditoria-transformadores-134/public/bases/Material_Pendente.xlsx
@@ -3751,7 +3751,7 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
-          <t>fora_da_janela</t>
+          <t>sem_interrupcao</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -7727,7 +7727,7 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr">
         <is>
-          <t>fora_da_janela</t>
+          <t>sem_interrupcao</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -10107,7 +10107,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>fora_da_janela</t>
+          <t>sem_interrupcao</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">

--- a/auditoria-transformadores-134/public/bases/Material_Pendente.xlsx
+++ b/auditoria-transformadores-134/public/bases/Material_Pendente.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" t="inlineStr"/>
     </row>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" t="inlineStr"/>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>EXCLUÍDA</t>
+          <t>SAÍDA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3533,11 +3533,7 @@
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>fora_da_janela</t>
-        </is>
-      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
           <t>AVARIADO</t>
